--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136021644</v>
       </c>
       <c r="B11" t="n">
-        <v>98198</v>
+        <v>98201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136021596</v>
       </c>
       <c r="B3" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136023776</v>
       </c>
       <c r="B4" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>136021644</v>
       </c>
       <c r="B11" t="n">
-        <v>98201</v>
+        <v>98202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 32151-2026 artfynd.xlsx
+++ b/artfynd/A 32151-2026 artfynd.xlsx
@@ -1228,7 +1228,7 @@
         <v>136136856</v>
       </c>
       <c r="B7" t="n">
-        <v>58019</v>
+        <v>58021</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>136136720</v>
       </c>
       <c r="B9" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136136941</v>
       </c>
       <c r="B10" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
